--- a/google_l6_prep_tracker.xlsx
+++ b/google_l6_prep_tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Progress" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Problems'!$A$1:$J$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Problems'!$A$1:$J$198</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Study Plan'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4602,25 +4602,25 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms</t>
+          <t>Kth Largest Element in an Array</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>215</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>LC 252</t>
+          <t>LC 215</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>MeetingRooms.java</t>
+          <t>KthLargestElementInAnArray.java</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -4655,20 +4655,20 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Merge Intervals</t>
+          <t>Meeting Rooms</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F86" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>252</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>LC 56</t>
+          <t>LC 252</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>MergeIntervals.java</t>
+          <t>MeetingRooms.java</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -4703,20 +4703,20 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Insert Interval</t>
+          <t>Merge Intervals</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>LC 57</t>
+          <t>LC 56</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>InsertInterval.java</t>
+          <t>MergeIntervals.java</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -4751,11 +4751,11 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms II</t>
+          <t>Insert Interval</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>253</v>
+        <v>57</v>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>LC 253</t>
+          <t>LC 57</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>MeetingRoomsII.java</t>
+          <t>InsertInterval.java</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -4799,20 +4799,20 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Minimum Time Difference</t>
+          <t>Meeting Rooms II</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>539</v>
+        <v>253</v>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>LC 539</t>
+          <t>LC 253</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>MinimumTimeDifference.java</t>
+          <t>MeetingRoomsII.java</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>My Calendar I</t>
+          <t>Minimum Time Difference</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>729</v>
+        <v>539</v>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>LC 729</t>
+          <t>LC 539</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>MyCalendarI.java</t>
+          <t>MinimumTimeDifference.java</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
@@ -4895,20 +4895,20 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms III</t>
+          <t>My Calendar I</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2402</v>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>729</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>LC 2402</t>
+          <t>LC 729</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>MeetingRoomsIII.java</t>
+          <t>MyCalendarI.java</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
@@ -4943,20 +4943,20 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Employee Free Time</t>
+          <t>Meeting Rooms III</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>759</v>
+        <v>2402</v>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>LC 759</t>
+          <t>LC 2402</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>EmployeeFreeTime.java</t>
+          <t>MeetingRoomsIII.java</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -4991,11 +4991,11 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Range Module</t>
+          <t>Employee Free Time</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>715</v>
+        <v>759</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>LC 715</t>
+          <t>LC 759</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>RangeModule.java</t>
+          <t>EmployeeFreeTime.java</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -5039,11 +5039,11 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>The Skyline Problem</t>
+          <t>Range Module</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>218</v>
+        <v>715</v>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>LC 218</t>
+          <t>LC 715</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>TheSkylineProblem.java</t>
+          <t>RangeModule.java</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -5082,25 +5082,25 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Subsets</t>
+          <t>The Skyline Problem</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F95" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>218</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>LC 78</t>
+          <t>LC 218</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Subsets.java</t>
+          <t>TheSkylineProblem.java</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Combination Sum</t>
+          <t>Subsets</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>LC 39</t>
+          <t>LC 78</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>CombinationSum.java</t>
+          <t>Subsets.java</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -5183,20 +5183,20 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Letter Combinations of a Phone Number</t>
+          <t>Combination Sum</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>LC 17</t>
+          <t>LC 39</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>LetterCombinations.java</t>
+          <t>CombinationSum.java</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -5231,11 +5231,11 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Generate Parentheses</t>
+          <t>Letter Combinations of a Phone Number</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>LC 22</t>
+          <t>LC 17</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>GenerateParentheses.java</t>
+          <t>LetterCombinations.java</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
@@ -5279,11 +5279,11 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Permutations</t>
+          <t>Generate Parentheses</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>LC 46</t>
+          <t>LC 22</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Permutations.java</t>
+          <t>GenerateParentheses.java</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
@@ -5327,20 +5327,20 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Confusing Number II</t>
+          <t>Permutations</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1088</v>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>46</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>LC 1088</t>
+          <t>LC 46</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>ConfusingNumberII.java</t>
+          <t>Permutations.java</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
@@ -5375,20 +5375,20 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>N-Queens</t>
+          <t>Confusing Number II</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>51</v>
+        <v>1088</v>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>LC 51</t>
+          <t>LC 1088</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>NQueens.java</t>
+          <t>ConfusingNumberII.java</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -5423,20 +5423,20 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Expression Add Operators</t>
+          <t>N-Queens</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>282</v>
+        <v>51</v>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>LC 282</t>
+          <t>LC 51</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>ExpressionAddOperators.java</t>
+          <t>NQueens.java</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
@@ -5471,11 +5471,11 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Robot Room Cleaner</t>
+          <t>Expression Add Operators</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>489</v>
+        <v>282</v>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>LC 489</t>
+          <t>LC 282</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>RobotRoomCleaner.java</t>
+          <t>ExpressionAddOperators.java</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
@@ -5514,25 +5514,25 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Spiral Matrix</t>
+          <t>Robot Room Cleaner</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>489</v>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>LC 54</t>
+          <t>LC 489</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>SpiralMatrix.java</t>
+          <t>RobotRoomCleaner.java</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -5567,11 +5567,11 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Rotate Image</t>
+          <t>Spiral Matrix</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>LC 48</t>
+          <t>LC 54</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>RotateImage.java</t>
+          <t>SpiralMatrix.java</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
@@ -5615,20 +5615,20 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Set Matrix Zeroes</t>
+          <t>Rotate Image</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F106" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>LC 73</t>
+          <t>LC 48</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>SetMatrixZeroes.java</t>
+          <t>RotateImage.java</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
@@ -5663,20 +5663,20 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Battleships in a Board</t>
+          <t>Set Matrix Zeroes</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>419</v>
+        <v>73</v>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>LC 419</t>
+          <t>LC 73</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Battleships.java</t>
+          <t>SetMatrixZeroes.java</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
@@ -5711,20 +5711,20 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Minimum Area Rectangle</t>
+          <t>Battleships in a Board</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>939</v>
+        <v>419</v>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>LC 939</t>
+          <t>LC 419</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>MinimumAreaRectangle.java</t>
+          <t>Battleships.java</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
@@ -5759,20 +5759,20 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Longest Line of Consecutive One in Matrix</t>
+          <t>Minimum Area Rectangle</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>562</v>
+        <v>939</v>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F109" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>LC 562</t>
+          <t>LC 939</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>LongestLineOfConsecutiveOne.java</t>
+          <t>MinimumAreaRectangle.java</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
@@ -5807,15 +5807,15 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Longest Increasing Path in a Matrix</t>
+          <t>Longest Line of Consecutive One in Matrix</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>562</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>LC 329</t>
+          <t>LC 562</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>LongestIncreasingPath.java</t>
+          <t>LongestLineOfConsecutiveOne.java</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
@@ -5850,25 +5850,25 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Flood Fill</t>
+          <t>Longest Increasing Path in a Matrix</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>733</v>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F111" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>329</v>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>LC 733</t>
+          <t>LC 329</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>FloodFill.java</t>
+          <t>LongestIncreasingPath.java</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -5903,20 +5903,20 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Number of Islands</t>
+          <t>Flood Fill</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>733</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>LC 200</t>
+          <t>LC 733</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>NumberOfIslands.java</t>
+          <t>FloodFill.java</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
@@ -5951,20 +5951,20 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Number of Closed Islands</t>
+          <t>Number of Islands</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1254</v>
+        <v>200</v>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F113" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>LC 1254</t>
+          <t>LC 200</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>NumberOfClosedIslands.java</t>
+          <t>NumberOfIslands.java</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
@@ -5999,20 +5999,20 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Clone Graph</t>
+          <t>Number of Closed Islands</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>133</v>
+        <v>1254</v>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>LC 133</t>
+          <t>LC 1254</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>CloneGraph.java</t>
+          <t>NumberOfClosedIslands.java</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
@@ -6047,20 +6047,20 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Number of Connected Components in an Undirected Graph</t>
+          <t>Clone Graph</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>323</v>
+        <v>133</v>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F115" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>LC 323</t>
+          <t>LC 133</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>NumberOfConnectedComponents.java</t>
+          <t>CloneGraph.java</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
@@ -6095,20 +6095,20 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Graph Valid Tree</t>
+          <t>Number of Connected Components in an Undirected Graph</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>LC 261</t>
+          <t>LC 323</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>GraphValidTree.java</t>
+          <t>NumberOfConnectedComponents.java</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -6143,11 +6143,11 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Graph Valid Tree</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>207</v>
+        <v>261</v>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>LC 207</t>
+          <t>LC 261</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>CourseSchedule.java</t>
+          <t>GraphValidTree.java</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
@@ -6191,20 +6191,20 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Alien Dictionary</t>
+          <t>Course Schedule</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F118" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>207</v>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>LC 269</t>
+          <t>LC 207</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>AlienDictionary.java</t>
+          <t>CourseSchedule.java</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -6239,20 +6239,20 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Pacific Atlantic Water Flow</t>
+          <t>Alien Dictionary</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>417</v>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>269</v>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>LC 417</t>
+          <t>LC 269</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>PacificAtlanticWaterFlow.java</t>
+          <t>AlienDictionary.java</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -6287,20 +6287,20 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Rotting Oranges</t>
+          <t>Pacific Atlantic Water Flow</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>994</v>
+        <v>417</v>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F120" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>LC 994</t>
+          <t>LC 417</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>RottingOranges.java</t>
+          <t>PacificAtlanticWaterFlow.java</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
@@ -6335,20 +6335,20 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>The Maze</t>
+          <t>Rotting Oranges</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>490</v>
+        <v>994</v>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>LC 490</t>
+          <t>LC 994</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>TheMaze.java</t>
+          <t>RottingOranges.java</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Accounts Merge</t>
+          <t>The Maze</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>721</v>
+        <v>490</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F122" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>LC 721</t>
+          <t>LC 490</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>AccountsMerge.java</t>
+          <t>TheMaze.java</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
@@ -6431,20 +6431,20 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>The Earliest Moment When Everyone Become Friends</t>
+          <t>Accounts Merge</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1101</v>
+        <v>721</v>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>LC 1101</t>
+          <t>LC 721</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>EarliestMomentEveryoneFriends.java</t>
+          <t>AccountsMerge.java</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -6479,20 +6479,20 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Word Ladder</t>
+          <t>The Earliest Moment When Everyone Become Friends</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>1101</v>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>LC 127</t>
+          <t>LC 1101</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>WordLadder.java</t>
+          <t>EarliestMomentEveryoneFriends.java</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
@@ -6527,20 +6527,20 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Shortest Distance from All Buildings</t>
+          <t>Word Ladder</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>317</v>
+        <v>127</v>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>LC 317</t>
+          <t>LC 127</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>ShortestDistanceFromAllBuildings.java</t>
+          <t>WordLadder.java</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -6575,11 +6575,11 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Swim in Rising Water</t>
+          <t>Shortest Distance from All Buildings</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>778</v>
+        <v>317</v>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
@@ -6598,12 +6598,12 @@
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>LC 778</t>
+          <t>LC 317</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>SwimInRisingWater.java</t>
+          <t>ShortestDistanceFromAllBuildings.java</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
@@ -6623,20 +6623,20 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Cheapest Flights Within K Stops</t>
+          <t>Swim in Rising Water</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>787</v>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>778</v>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>LC 787</t>
+          <t>LC 778</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>CheapestFlightsWithinKStops.java</t>
+          <t>SwimInRisingWater.java</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -6671,20 +6671,20 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Race Car</t>
+          <t>Cheapest Flights Within K Stops</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>818</v>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F128" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>787</v>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>LC 818</t>
+          <t>LC 787</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>RaceCar.java</t>
+          <t>CheapestFlightsWithinKStops.java</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -6714,25 +6714,25 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Network Delay Time</t>
+          <t>Race Car</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>743</v>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F129" s="15" t="inlineStr">
-        <is>
-          <t>L6 differentiator</t>
+        <v>818</v>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>LC 743</t>
+          <t>LC 818</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>NetworkDelayTime.java</t>
+          <t>RaceCar.java</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -6762,25 +6762,25 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Detonate the Maximum Bombs</t>
+          <t>Reconstruct Itinerary</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>2101</v>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F130" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>332</v>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>LC 2101</t>
+          <t>LC 332</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>DetonateTheMaximumBombs.java</t>
+          <t>ReconstructItinerary.java</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
@@ -6815,20 +6815,20 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Minimum Time to Visit a Cell In a Grid</t>
+          <t>Network Delay Time</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2577</v>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>743</v>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F131" s="15" t="inlineStr">
+        <is>
+          <t>L6 differentiator</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>LC 2577</t>
+          <t>LC 743</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>MinimumTimeToVisitCell.java</t>
+          <t>NetworkDelayTime.java</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
@@ -6863,15 +6863,15 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Number of Good Paths</t>
+          <t>Detonate the Maximum Bombs</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2421</v>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>2101</v>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>LC 2421</t>
+          <t>LC 2101</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>NumberOfGoodPaths.java</t>
+          <t>DetonateTheMaximumBombs.java</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
@@ -6911,20 +6911,20 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Critical Connections in a Network</t>
+          <t>Minimum Time to Visit a Cell In a Grid</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1192</v>
+        <v>2577</v>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F133" s="15" t="inlineStr">
-        <is>
-          <t>L6 differentiator</t>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>LC 1192</t>
+          <t>LC 2577</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>CriticalConnections.java</t>
+          <t>MinimumTimeToVisitCell.java</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -6959,20 +6959,20 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Cat and Mouse</t>
+          <t>Number of Good Paths</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>913</v>
+        <v>2421</v>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F134" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>LC 913</t>
+          <t>LC 2421</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>CatAndMouse.java</t>
+          <t>NumberOfGoodPaths.java</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
@@ -7002,25 +7002,25 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>🤑 Greedy</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Gas Station</t>
+          <t>Critical Connections in a Network</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>1192</v>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F135" s="15" t="inlineStr">
+        <is>
+          <t>L6 differentiator</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>LC 134</t>
+          <t>LC 1192</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>GasStation.java</t>
+          <t>CriticalConnections.java</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
@@ -7050,25 +7050,25 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>🤑 Greedy</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Task Scheduler</t>
+          <t>Cat and Mouse</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>621</v>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F136" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>913</v>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>LC 621</t>
+          <t>LC 913</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>TaskScheduler.java</t>
+          <t>CatAndMouse.java</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -7103,22 +7103,20 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Huffman Coding</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F137" s="16" t="inlineStr">
-        <is>
-          <t>Reported L6</t>
+          <t>Gas Station</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7126,14 +7124,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>LC 134</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>HuffmanCoding.java</t>
+          <t>GasStation.java</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
@@ -7148,25 +7146,25 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🤑 Greedy</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Climbing Stairs</t>
+          <t>Task Scheduler</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>621</v>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7176,12 +7174,12 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>LC 70</t>
+          <t>LC 621</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>ClimbingStairs.java</t>
+          <t>TaskScheduler.java</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
@@ -7196,25 +7194,27 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🤑 Greedy</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>House Robber</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+          <t>Huffman Coding</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F139" s="16" t="inlineStr">
+        <is>
+          <t>Reported L6</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7222,14 +7222,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>LC 198</t>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>HouseRobber.java</t>
+          <t>HuffmanCoding.java</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -7249,15 +7249,15 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>House Robber II</t>
+          <t>Climbing Stairs</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>70</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>LC 213</t>
+          <t>LC 70</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>HouseRobberII.java</t>
+          <t>ClimbingStairs.java</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
@@ -7297,11 +7297,11 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Jump Game</t>
+          <t>House Robber</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
@@ -7320,12 +7320,12 @@
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>LC 55</t>
+          <t>LC 198</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>JumpGame.java</t>
+          <t>HouseRobber.java</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
@@ -7345,20 +7345,20 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Jump Game II</t>
+          <t>House Robber II</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>LC 45</t>
+          <t>LC 213</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>JumpGameII.java</t>
+          <t>HouseRobberII.java</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
@@ -7393,20 +7393,20 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Coin Change</t>
+          <t>Jump Game</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>322</v>
+        <v>55</v>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>LC 322</t>
+          <t>LC 55</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>CoinChange.java</t>
+          <t>JumpGame.java</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -7441,11 +7441,11 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Coin Change II</t>
+          <t>Jump Game II</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>518</v>
+        <v>45</v>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>LC 518</t>
+          <t>LC 45</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>CoinChangeII.java</t>
+          <t>JumpGameII.java</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
@@ -7489,20 +7489,20 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Word Break</t>
+          <t>Coin Change</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>139</v>
+        <v>322</v>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>LC 139</t>
+          <t>LC 322</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>WordBreak.java</t>
+          <t>CoinChange.java</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
@@ -7537,20 +7537,20 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Decode Ways</t>
+          <t>Coin Change II</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>91</v>
+        <v>518</v>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>LC 91</t>
+          <t>LC 518</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>DecodeWays.java</t>
+          <t>CoinChangeII.java</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
@@ -7585,20 +7585,20 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Longest Increasing Subsequence</t>
+          <t>Word Break</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>300</v>
+        <v>139</v>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F147" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>LC 300</t>
+          <t>LC 139</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>LongestIncreasingSubsequence.java</t>
+          <t>WordBreak.java</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
@@ -7633,11 +7633,11 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Unique Paths</t>
+          <t>Decode Ways</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>LC 62</t>
+          <t>LC 91</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>UniquePaths.java</t>
+          <t>DecodeWays.java</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
@@ -7681,20 +7681,20 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Unique Paths II</t>
+          <t>Longest Increasing Subsequence</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F149" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>LC 63</t>
+          <t>LC 300</t>
         </is>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>UniquePathsII.java</t>
+          <t>LongestIncreasingSubsequence.java</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
@@ -7729,20 +7729,20 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Maximal Square</t>
+          <t>Unique Paths</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F150" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>LC 221</t>
+          <t>LC 62</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>MaximalSquare.java</t>
+          <t>UniquePaths.java</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
@@ -7777,20 +7777,20 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Longest Common Subsequence</t>
+          <t>Unique Paths II</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1143</v>
+        <v>63</v>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>LC 1143</t>
+          <t>LC 63</t>
         </is>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>LongestCommonSubsequence.java</t>
+          <t>UniquePathsII.java</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
@@ -7825,20 +7825,20 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Edit Distance</t>
+          <t>Maximal Square</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>72</v>
+        <v>221</v>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F152" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>LC 72</t>
+          <t>LC 221</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>EditDistance.java</t>
+          <t>MaximalSquare.java</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -7873,20 +7873,20 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Student Attendance Record II</t>
+          <t>Longest Common Subsequence</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>552</v>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F153" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>1143</v>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>LC 552</t>
+          <t>LC 1143</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>StudentAttendanceRecordII.java</t>
+          <t>LongestCommonSubsequence.java</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
@@ -7921,20 +7921,20 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Poor Pigs</t>
+          <t>Edit Distance</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>458</v>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>72</v>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>LC 458</t>
+          <t>LC 72</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>PoorPigs.java</t>
+          <t>EditDistance.java</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
@@ -7964,25 +7964,25 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Counting Bits</t>
+          <t>Student Attendance Record II</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F155" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>552</v>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>LC 338</t>
+          <t>LC 552</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>CountingBits.java</t>
+          <t>StudentAttendanceRecordII.java</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
@@ -8012,25 +8012,25 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sum of Two Integers</t>
+          <t>Poor Pigs</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>371</v>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F156" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>458</v>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>LC 371</t>
+          <t>LC 458</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>SumOfTwoIntegers.java</t>
+          <t>PoorPigs.java</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
@@ -8060,20 +8060,20 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Pow(x, n)</t>
+          <t>Numbers At Most N Given Digit Set</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>902</v>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>LC 50</t>
+          <t>LC 902</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>PowXN.java</t>
+          <t>NumbersAtMostNGivenDigitSet.java</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
@@ -8113,20 +8113,20 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Linked List Random Node</t>
+          <t>Counting Bits</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>382</v>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>338</v>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F158" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>LC 382</t>
+          <t>LC 338</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>LinkedListRandomNode.java</t>
+          <t>CountingBits.java</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -8161,20 +8161,20 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Random Pick with Weight</t>
+          <t>Sum of Two Integers</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>528</v>
+        <v>371</v>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F159" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>LC 528</t>
+          <t>LC 371</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>RandomPickWithWeight.java</t>
+          <t>SumOfTwoIntegers.java</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
@@ -8204,16 +8204,16 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>🌴 Segment Tree / BIT</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Range Sum Query - Mutable</t>
+          <t>Pow(x, n)</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>307</v>
+        <v>50</v>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>LC 307</t>
+          <t>LC 50</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>RangeSumQueryMutable.java</t>
+          <t>PowXN.java</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
@@ -8252,25 +8252,25 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>🌴 Segment Tree / BIT</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Count of Range Sum</t>
+          <t>Linked List Random Node</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F161" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>382</v>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>LC 327</t>
+          <t>LC 382</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>CountOfRangeSum.java</t>
+          <t>LinkedListRandomNode.java</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
@@ -8300,25 +8300,25 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Min Stack</t>
+          <t>Random Pick with Weight</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>155</v>
+        <v>528</v>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F162" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>LC 155</t>
+          <t>LC 528</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>MinStack.java</t>
+          <t>RandomPickWithWeight.java</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
@@ -8348,25 +8348,25 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Stock Price Fluctuation</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>2034</v>
+        <v>204</v>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>LC 2034</t>
+          <t>LC 204</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>StockPriceFluctuation.java</t>
+          <t>CountPrimes.java</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
@@ -8396,25 +8396,25 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Detect Squares</t>
+          <t>Greatest Common Divisor of Strings</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F164" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>1071</v>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>LC 2013</t>
+          <t>LC 1071</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>DetectSquares.java</t>
+          <t>GreatestCommonDivisorOfStrings.java</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
@@ -8444,25 +8444,25 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Design Twitter</t>
+          <t>Maximum XOR of Two Numbers in an Array</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>355</v>
+        <v>421</v>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F165" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>LC 355</t>
+          <t>LC 421</t>
         </is>
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>DesignTwitter.java</t>
+          <t>MaximumXorOfTwoNumbers.java</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
@@ -8492,52 +8492,1588 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
+          <t>🌴 Segment Tree / BIT</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Range Sum Query - Mutable</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>LC 307</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>RangeSumQueryMutable.java</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>🌴 Segment Tree / BIT</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Count of Range Sum</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>LC 327</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>CountOfRangeSum.java</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>🏗️ Design</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Min Stack</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>LC 155</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>MinStack.java</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Stock Price Fluctuation</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>2034</v>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>LC 2034</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>StockPriceFluctuation.java</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Detect Squares</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>LC 2013</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>DetectSquares.java</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Design Twitter</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>LC 355</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>DesignTwitter.java</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>LFU Cache</t>
         </is>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D172" s="2" t="n">
         <v>460</v>
       </c>
-      <c r="E166" s="7" t="inlineStr">
+      <c r="E172" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F166" s="8" t="inlineStr">
+      <c r="F172" s="8" t="inlineStr">
         <is>
           <t>Google fav</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H166" s="5" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
         <is>
           <t>LC 460</t>
         </is>
       </c>
-      <c r="I166" s="5" t="inlineStr">
+      <c r="I172" s="5" t="inlineStr">
         <is>
           <t>LFUCache.java</t>
         </is>
       </c>
-      <c r="J166" s="5" t="inlineStr">
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Array</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>1146</v>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>LC 1146</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>SnapshotArray.java</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Insert Delete GetRandom O(1)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F174" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>LC 380</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>InsertDeleteGetRandomO1.java</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Time Based Key-Value Store</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>981</v>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>LC 981</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>TimeBasedKeyValueStore.java</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>🏗️ Design</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Design Hit Counter</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>LC 362</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>DesignHitCounter.java</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>🎭 Bitmask / Subset DP</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Shortest Path Visiting All Nodes</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>847</v>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F177" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>LC 847</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>ShortestPathVisitingAllNodes.java</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>🎭 Bitmask / Subset DP</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Partition to K Equal Sum Subsets</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>LC 698</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>PartitionToKEqualSumSubsets.java</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>🎭 Bitmask / Subset DP</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Smallest Sufficient Team</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>LC 1125</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>SmallestSufficientTeam.java</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>🎈 Interval DP</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Burst Balloons</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>LC 312</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>BurstBalloons.java</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>🎈 Interval DP</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Stone Game</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>LC 877</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>StoneGame.java</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>🎈 Interval DP</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Minimum Cost to Cut a Stick</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>1547</v>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>LC 1547</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>MinimumCostToCutAStick.java</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Partition Equal Subset Sum</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>LC 416</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>PartitionEqualSubsetSum.java</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Target Sum</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F184" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>LC 494</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>TargetSum.java</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>🌉 Minimum Spanning Tree</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Min Cost to Connect All Points</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1584</v>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>LC 1584</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>MinCostToConnectAllPoints.java</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>🌉 Minimum Spanning Tree</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Connecting Cities With Minimum Cost</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>1135</v>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F186" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>LC 1135</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>ConnectingCitiesWithMinimumCost.java</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>🧬 String Matching</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Repeated DNA Sequences</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F187" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>LC 187</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>RepeatedDNASequences.java</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>🧬 String Matching</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Shortest Palindrome</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>LC 214</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>ShortestPalindrome.java</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>🧬 String Matching</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Longest Duplicate Substring</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>LC 1044</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>LongestDuplicateSubstring.java</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>🎄 Tree DP / Rerooting</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>House Robber III</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>LC 337</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>HouseRobberIII.java</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>🎄 Tree DP / Rerooting</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Binary Tree Cameras</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>968</v>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>LC 968</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>BinaryTreeCameras.java</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>🎄 Tree DP / Rerooting</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Sum of Distances in Tree</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>LC 834</t>
+        </is>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>SumOfDistancesInTree.java</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>📊 2D Prefix Sum</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Range Sum Query 2D - Immutable</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>LC 304</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>RangeSumQuery2DImmutable.java</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>📊 2D Prefix Sum</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Range Sum Query 2D - Mutable</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F194" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>LC 308</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>RangeSumQuery2DMutable.java</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>➕ Difference Array</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Flight Bookings</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F195" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>LC 1109</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>CorporateFlightBookings.java</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>➕ Difference Array</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Car Pooling</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F196" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>LC 1094</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>CarPooling.java</t>
+        </is>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>🗂️ Ordered-Set / Stream</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Contains Duplicate III</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F197" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>LC 220</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
+          <t>ContainsDuplicateIII.java</t>
+        </is>
+      </c>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>🗂️ Ordered-Set / Stream</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Sliding Window Median</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F198" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>LC 480</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>SlidingWindowMedian.java</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J166"/>
+  <autoFilter ref="A1:J198"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G198" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Studying,Solved,Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8946,12 +10482,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId411"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId412"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId413"/>
@@ -9035,6 +10571,102 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId491"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId492"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId589"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9729,7 +11361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C44"/>
+  <dimension ref="B2:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -9750,7 +11382,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>165</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -9768,7 +11400,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -9778,7 +11410,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
@@ -9788,7 +11420,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -9816,7 +11448,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -9836,7 +11468,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -9846,7 +11478,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -9856,7 +11488,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -9876,7 +11508,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -10014,7 +11646,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -10054,7 +11686,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -10084,7 +11716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -10094,7 +11726,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -10114,7 +11746,97 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>🎭 Bitmask / Subset DP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>🎈 Interval DP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🌉 Minimum Spanning Tree</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>🧬 String Matching</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>🎄 Tree DP / Rerooting</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>📊 2D Prefix Sum</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>➕ Difference Array</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>🗂️ Ordered-Set / Stream</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/google_l6_prep_tracker.xlsx
+++ b/google_l6_prep_tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Progress" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Problems'!$A$1:$J$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Problems'!$A$1:$J$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Study Plan'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3306,20 +3306,20 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Reverse Linked List</t>
+          <t>Search a 2D Matrix</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>74</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>LC 206</t>
+          <t>LC 74</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ReverseLinkedList.java</t>
+          <t>SearchA2DMatrix.java</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -3354,25 +3354,25 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Merge Two Sorted Lists</t>
+          <t>Search a 2D Matrix II</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>240</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>LC 21</t>
+          <t>LC 240</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>MergeTwoSortedLists.java</t>
+          <t>SearchA2DMatrixII.java</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -3402,25 +3402,25 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Linked List Cycle</t>
+          <t>Search in Rotated Sorted Array II</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>81</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>LC 141</t>
+          <t>LC 81</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>DetectCycle.java</t>
+          <t>SearchInRotatedSortedArrayII.java</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -3450,25 +3450,25 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Palindrome Linked List</t>
+          <t>Find the Duplicate Number</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>287</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>LC 234</t>
+          <t>LC 287</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>PalindromeLinkedList.java</t>
+          <t>FindTheDuplicateNumber.java</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Remove Nth Node From End of List</t>
+          <t>Capacity To Ship Packages Within D Days</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>19</v>
+        <v>1011</v>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>LC 19</t>
+          <t>LC 1011</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>RemoveNthNodeFromEnd.java</t>
+          <t>CapacityToShipPackagesWithinDDays.java</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -3546,16 +3546,16 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>🔗 Linked Lists</t>
+          <t>🔎 Binary Search</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Add Two Numbers</t>
+          <t>Find K Closest Elements</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>658</v>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>LC 2</t>
+          <t>LC 658</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>AddTwoNumbers.java</t>
+          <t>FindKClosestElements.java</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -3599,15 +3599,15 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Reorder List</t>
+          <t>Reverse Linked List</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>206</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>LC 143</t>
+          <t>LC 206</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ReorderList.java</t>
+          <t>ReverseLinkedList.java</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -3647,20 +3647,20 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Copy List with Random Pointer</t>
+          <t>Merge Two Sorted Lists</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>21</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>LC 138</t>
+          <t>LC 21</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>CopyListWithRandomPointer.java</t>
+          <t>MergeTwoSortedLists.java</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -3695,15 +3695,15 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Merge k Sorted Lists</t>
+          <t>Linked List Cycle</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>141</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>LC 23</t>
+          <t>LC 141</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>MergeKSortedLists.java</t>
+          <t>DetectCycle.java</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -3743,20 +3743,20 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LRU Cache</t>
+          <t>Palindrome Linked List</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>234</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>LC 146</t>
+          <t>LC 234</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>LRUCache.java</t>
+          <t>PalindromeLinkedList.java</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
@@ -3786,25 +3786,25 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Binary Tree Level Order Traversal</t>
+          <t>Remove Nth Node From End of List</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>LC 102</t>
+          <t>LC 19</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>BinaryTreeLevelOrderTraversal.java</t>
+          <t>RemoveNthNodeFromEnd.java</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
@@ -3834,25 +3834,25 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Binary Tree Right Side View</t>
+          <t>Add Two Numbers</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>LC 199</t>
+          <t>LC 2</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>BinaryTreeRightSideView.java</t>
+          <t>AddTwoNumbers.java</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -3882,16 +3882,16 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Validate Binary Search Tree</t>
+          <t>Reorder List</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>LC 98</t>
+          <t>LC 143</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>ValidateBinarySearchTree.java</t>
+          <t>ReorderList.java</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
@@ -3930,25 +3930,25 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Lowest Common Ancestor of a Binary Tree</t>
+          <t>Copy List with Random Pointer</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>LC 236</t>
+          <t>LC 138</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>LowestCommonAncestor.java</t>
+          <t>CopyListWithRandomPointer.java</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
@@ -3978,25 +3978,25 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Flatten Binary Tree to Linked List</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>23</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>LC 114</t>
+          <t>LC 23</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>FlattenBinaryTreeToLinkedList.java</t>
+          <t>MergeKSortedLists.java</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -4026,25 +4026,25 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>🌳 Trees</t>
+          <t>🔗 Linked Lists</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Find Leaves of Binary Tree</t>
+          <t>LRU Cache</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>366</v>
+        <v>146</v>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>LC 366</t>
+          <t>LC 146</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>FindLeavesOfBinaryTree.java</t>
+          <t>LRUCache.java</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -4079,20 +4079,20 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Step-By-Step Directions From a Binary Tree Node to Another</t>
+          <t>Binary Tree Level Order Traversal</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2096</v>
+        <v>102</v>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>LC 2096</t>
+          <t>LC 102</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>StepByStepDirections.java</t>
+          <t>BinaryTreeLevelOrderTraversal.java</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -4127,20 +4127,20 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Binary Tree Maximum Path Sum</t>
+          <t>Binary Tree Right Side View</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>199</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>LC 124</t>
+          <t>LC 199</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>BinaryTreeMaximumPathSum.java</t>
+          <t>BinaryTreeRightSideView.java</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -4175,20 +4175,20 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Serialize and Deserialize Binary Tree</t>
+          <t>Validate Binary Search Tree</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>98</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>LC 297</t>
+          <t>LC 98</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>SerializeAndDeserializeBinaryTree.java</t>
+          <t>ValidateBinarySearchTree.java</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -4218,16 +4218,16 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>🌲 Tries</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Implement Trie (Prefix Tree)</t>
+          <t>Lowest Common Ancestor of a Binary Tree</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>LC 208</t>
+          <t>LC 236</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>ImplementTrie.java</t>
+          <t>LowestCommonAncestor.java</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -4266,25 +4266,25 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>🌲 Tries</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Logger Rate Limiter</t>
+          <t>Flatten Binary Tree to Linked List</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>359</v>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>114</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>LC 359</t>
+          <t>LC 114</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>LoggerRateLimiter.java</t>
+          <t>FlattenBinaryTreeToLinkedList.java</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
@@ -4314,25 +4314,25 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>🌲 Tries</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Word Search II</t>
+          <t>Find Leaves of Binary Tree</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>366</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>LC 212</t>
+          <t>LC 366</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>WordSearchII.java</t>
+          <t>FindLeavesOfBinaryTree.java</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -4362,25 +4362,25 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Top K Frequent Elements</t>
+          <t>Step-By-Step Directions From a Binary Tree Node to Another</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>347</v>
+        <v>2096</v>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>LC 347</t>
+          <t>LC 2096</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>TopKFrequentElements.java</t>
+          <t>StepByStepDirections.java</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
@@ -4410,25 +4410,25 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>K Closest Points to Origin</t>
+          <t>Binary Tree Maximum Path Sum</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>973</v>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>124</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>LC 973</t>
+          <t>LC 124</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>KClosestPointsToOrigin.java</t>
+          <t>BinaryTreeMaximumPathSum.java</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
@@ -4458,25 +4458,25 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌳 Trees</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Sliding Window Maximum</t>
+          <t>Serialize and Deserialize Binary Tree</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>239</v>
+        <v>297</v>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>LC 239</t>
+          <t>LC 297</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>SlidingWindowMaximum.java</t>
+          <t>SerializeAndDeserializeBinaryTree.java</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
@@ -4506,25 +4506,25 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌲 Tries</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Find Median from Data Stream</t>
+          <t>Implement Trie (Prefix Tree)</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>208</v>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>LC 295</t>
+          <t>LC 208</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>FindMedianFromDataStream.java</t>
+          <t>ImplementTrie.java</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
@@ -4554,25 +4554,25 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌲 Tries</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Finding MK Average</t>
+          <t>Logger Rate Limiter</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1825</v>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="inlineStr">
-        <is>
-          <t>Recent 2025-26</t>
+        <v>359</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>LC 1825</t>
+          <t>LC 359</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>FindingMKAverage.java</t>
+          <t>LoggerRateLimiter.java</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
@@ -4602,25 +4602,25 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>⛰️ Heap / Priority Queue</t>
+          <t>🌲 Tries</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Kth Largest Element in an Array</t>
+          <t>Word Search II</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>212</v>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>LC 215</t>
+          <t>LC 212</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>KthLargestElementInAnArray.java</t>
+          <t>WordSearchII.java</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -4650,20 +4650,20 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms</t>
+          <t>Top K Frequent Elements</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>347</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>LC 252</t>
+          <t>LC 347</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>MeetingRooms.java</t>
+          <t>TopKFrequentElements.java</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -4698,25 +4698,25 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Merge Intervals</t>
+          <t>K Closest Points to Origin</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>56</v>
+        <v>973</v>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F87" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>LC 56</t>
+          <t>LC 973</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>MergeIntervals.java</t>
+          <t>KClosestPointsToOrigin.java</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -4746,25 +4746,25 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Insert Interval</t>
+          <t>Sliding Window Maximum</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>239</v>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>LC 57</t>
+          <t>LC 239</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>InsertInterval.java</t>
+          <t>SlidingWindowMaximum.java</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -4794,25 +4794,25 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms II</t>
+          <t>Find Median from Data Stream</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>253</v>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>295</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>LC 253</t>
+          <t>LC 295</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>MeetingRoomsII.java</t>
+          <t>FindMedianFromDataStream.java</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -4842,25 +4842,25 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Minimum Time Difference</t>
+          <t>Finding MK Average</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>539</v>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>1825</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>Recent 2025-26</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>LC 539</t>
+          <t>LC 1825</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>MinimumTimeDifference.java</t>
+          <t>FindingMKAverage.java</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
@@ -4890,25 +4890,25 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>📅 Intervals &amp; Line Sweep</t>
+          <t>⛰️ Heap / Priority Queue</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>My Calendar I</t>
+          <t>Kth Largest Element in an Array</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>729</v>
+        <v>215</v>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>LC 729</t>
+          <t>LC 215</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>MyCalendarI.java</t>
+          <t>KthLargestElementInAnArray.java</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
@@ -4943,20 +4943,20 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Meeting Rooms III</t>
+          <t>Meeting Rooms</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2402</v>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>252</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>LC 2402</t>
+          <t>LC 252</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>MeetingRoomsIII.java</t>
+          <t>MeetingRooms.java</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
@@ -4991,20 +4991,20 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Employee Free Time</t>
+          <t>Merge Intervals</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>759</v>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>56</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>LC 759</t>
+          <t>LC 56</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>EmployeeFreeTime.java</t>
+          <t>MergeIntervals.java</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -5039,20 +5039,20 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Range Module</t>
+          <t>Insert Interval</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>715</v>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>57</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>LC 715</t>
+          <t>LC 57</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>RangeModule.java</t>
+          <t>InsertInterval.java</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -5087,20 +5087,20 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>The Skyline Problem</t>
+          <t>Meeting Rooms II</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>218</v>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>253</v>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>LC 218</t>
+          <t>LC 253</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>TheSkylineProblem.java</t>
+          <t>MeetingRoomsII.java</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
@@ -5130,25 +5130,25 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Subsets</t>
+          <t>Minimum Time Difference</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F96" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>LC 78</t>
+          <t>LC 539</t>
         </is>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Subsets.java</t>
+          <t>MinimumTimeDifference.java</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
@@ -5178,25 +5178,25 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Combination Sum</t>
+          <t>My Calendar I</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>39</v>
+        <v>729</v>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>LC 39</t>
+          <t>LC 729</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>CombinationSum.java</t>
+          <t>MyCalendarI.java</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Letter Combinations of a Phone Number</t>
+          <t>Meeting Rooms III</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>2402</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>LC 17</t>
+          <t>LC 2402</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>LetterCombinations.java</t>
+          <t>MeetingRoomsIII.java</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
@@ -5274,25 +5274,25 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Generate Parentheses</t>
+          <t>Employee Free Time</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>759</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>LC 22</t>
+          <t>LC 759</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>GenerateParentheses.java</t>
+          <t>EmployeeFreeTime.java</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
@@ -5322,25 +5322,25 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Permutations</t>
+          <t>Range Module</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>715</v>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>LC 46</t>
+          <t>LC 715</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Permutations.java</t>
+          <t>RangeModule.java</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
@@ -5370,25 +5370,25 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>🔙 Backtracking</t>
+          <t>📅 Intervals &amp; Line Sweep</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Confusing Number II</t>
+          <t>The Skyline Problem</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1088</v>
+        <v>218</v>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>LC 1088</t>
+          <t>LC 218</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>ConfusingNumberII.java</t>
+          <t>TheSkylineProblem.java</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -5423,20 +5423,20 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>N-Queens</t>
+          <t>Subsets</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>78</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>LC 51</t>
+          <t>LC 78</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>NQueens.java</t>
+          <t>Subsets.java</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
@@ -5471,20 +5471,20 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Expression Add Operators</t>
+          <t>Combination Sum</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>282</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F103" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>39</v>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>LC 282</t>
+          <t>LC 39</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>ExpressionAddOperators.java</t>
+          <t>CombinationSum.java</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
@@ -5519,20 +5519,20 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Robot Room Cleaner</t>
+          <t>Letter Combinations of a Phone Number</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>489</v>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>17</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>LC 489</t>
+          <t>LC 17</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>RobotRoomCleaner.java</t>
+          <t>LetterCombinations.java</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -5562,25 +5562,25 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Spiral Matrix</t>
+          <t>Generate Parentheses</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>LC 54</t>
+          <t>LC 22</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>SpiralMatrix.java</t>
+          <t>GenerateParentheses.java</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
@@ -5610,25 +5610,25 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Rotate Image</t>
+          <t>Permutations</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>LC 48</t>
+          <t>LC 46</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>RotateImage.java</t>
+          <t>Permutations.java</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
@@ -5658,25 +5658,25 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Set Matrix Zeroes</t>
+          <t>Confusing Number II</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>1088</v>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>LC 73</t>
+          <t>LC 1088</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>SetMatrixZeroes.java</t>
+          <t>ConfusingNumberII.java</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
@@ -5706,25 +5706,25 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Battleships in a Board</t>
+          <t>N-Queens</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>419</v>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F108" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>51</v>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>LC 419</t>
+          <t>LC 51</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Battleships.java</t>
+          <t>NQueens.java</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
@@ -5754,25 +5754,25 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Minimum Area Rectangle</t>
+          <t>Expression Add Operators</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>939</v>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>282</v>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>LC 939</t>
+          <t>LC 282</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>MinimumAreaRectangle.java</t>
+          <t>ExpressionAddOperators.java</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
@@ -5802,20 +5802,20 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>🔲 Matrix</t>
+          <t>🔙 Backtracking</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Longest Line of Consecutive One in Matrix</t>
+          <t>Robot Room Cleaner</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>562</v>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>489</v>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>LC 562</t>
+          <t>LC 489</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>LongestLineOfConsecutiveOne.java</t>
+          <t>RobotRoomCleaner.java</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
@@ -5855,20 +5855,20 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Longest Increasing Path in a Matrix</t>
+          <t>Spiral Matrix</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>329</v>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F111" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>54</v>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>LC 329</t>
+          <t>LC 54</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>LongestIncreasingPath.java</t>
+          <t>SpiralMatrix.java</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -5898,25 +5898,25 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Flood Fill</t>
+          <t>Rotate Image</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>733</v>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F112" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>48</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>LC 733</t>
+          <t>LC 48</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>FloodFill.java</t>
+          <t>RotateImage.java</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
@@ -5946,25 +5946,25 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Number of Islands</t>
+          <t>Set Matrix Zeroes</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>LC 200</t>
+          <t>LC 73</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>NumberOfIslands.java</t>
+          <t>SetMatrixZeroes.java</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
@@ -5994,25 +5994,25 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Number of Closed Islands</t>
+          <t>Battleships in a Board</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1254</v>
+        <v>419</v>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F114" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>LC 1254</t>
+          <t>LC 419</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>NumberOfClosedIslands.java</t>
+          <t>Battleships.java</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
@@ -6042,25 +6042,25 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Clone Graph</t>
+          <t>Minimum Area Rectangle</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>133</v>
+        <v>939</v>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>LC 133</t>
+          <t>LC 939</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>CloneGraph.java</t>
+          <t>MinimumAreaRectangle.java</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
@@ -6090,25 +6090,25 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Number of Connected Components in an Undirected Graph</t>
+          <t>Longest Line of Consecutive One in Matrix</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>323</v>
+        <v>562</v>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F116" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>LC 323</t>
+          <t>LC 562</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>NumberOfConnectedComponents.java</t>
+          <t>LongestLineOfConsecutiveOne.java</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
@@ -6138,25 +6138,25 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>🕸️ Graphs</t>
+          <t>🔲 Matrix</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Graph Valid Tree</t>
+          <t>Longest Increasing Path in a Matrix</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>261</v>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>329</v>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>LC 261</t>
+          <t>LC 329</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>GraphValidTree.java</t>
+          <t>LongestIncreasingPath.java</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
@@ -6191,20 +6191,20 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Flood Fill</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>733</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>LC 207</t>
+          <t>LC 733</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>CourseSchedule.java</t>
+          <t>FloodFill.java</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -6239,20 +6239,20 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Alien Dictionary</t>
+          <t>Number of Islands</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F119" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>200</v>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>LC 269</t>
+          <t>LC 200</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>AlienDictionary.java</t>
+          <t>NumberOfIslands.java</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -6287,20 +6287,20 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Pacific Atlantic Water Flow</t>
+          <t>Number of Closed Islands</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>417</v>
+        <v>1254</v>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>LC 417</t>
+          <t>LC 1254</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>PacificAtlanticWaterFlow.java</t>
+          <t>NumberOfClosedIslands.java</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
@@ -6335,20 +6335,20 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Rotting Oranges</t>
+          <t>Clone Graph</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>994</v>
+        <v>133</v>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F121" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>LC 994</t>
+          <t>LC 133</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>RottingOranges.java</t>
+          <t>CloneGraph.java</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -6383,20 +6383,20 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>The Maze</t>
+          <t>Number of Connected Components in an Undirected Graph</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>490</v>
+        <v>323</v>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>LC 490</t>
+          <t>LC 323</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>TheMaze.java</t>
+          <t>NumberOfConnectedComponents.java</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
@@ -6431,20 +6431,20 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Accounts Merge</t>
+          <t>Graph Valid Tree</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>721</v>
+        <v>261</v>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>LC 721</t>
+          <t>LC 261</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>AccountsMerge.java</t>
+          <t>GraphValidTree.java</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
@@ -6479,20 +6479,20 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>The Earliest Moment When Everyone Become Friends</t>
+          <t>Course Schedule</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1101</v>
+        <v>207</v>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>LC 1101</t>
+          <t>LC 207</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>EarliestMomentEveryoneFriends.java</t>
+          <t>CourseSchedule.java</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
@@ -6527,20 +6527,20 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Word Ladder</t>
+          <t>Alien Dictionary</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>127</v>
+        <v>269</v>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F125" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>LC 127</t>
+          <t>LC 269</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>WordLadder.java</t>
+          <t>AlienDictionary.java</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -6575,20 +6575,20 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Shortest Distance from All Buildings</t>
+          <t>Pacific Atlantic Water Flow</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>317</v>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>417</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>LC 317</t>
+          <t>LC 417</t>
         </is>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>ShortestDistanceFromAllBuildings.java</t>
+          <t>PacificAtlanticWaterFlow.java</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
@@ -6623,20 +6623,20 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Swim in Rising Water</t>
+          <t>Rotting Oranges</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>778</v>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F127" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>994</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>LC 778</t>
+          <t>LC 994</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>SwimInRisingWater.java</t>
+          <t>RottingOranges.java</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
@@ -6671,20 +6671,20 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Cheapest Flights Within K Stops</t>
+          <t>The Maze</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>787</v>
+        <v>490</v>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F128" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>LC 787</t>
+          <t>LC 490</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>CheapestFlightsWithinKStops.java</t>
+          <t>TheMaze.java</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
@@ -6719,20 +6719,20 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Race Car</t>
+          <t>Accounts Merge</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>818</v>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F129" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>721</v>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>LC 818</t>
+          <t>LC 721</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>RaceCar.java</t>
+          <t>AccountsMerge.java</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -6767,20 +6767,20 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Reconstruct Itinerary</t>
+          <t>The Earliest Moment When Everyone Become Friends</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>1101</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>LC 332</t>
+          <t>LC 1101</t>
         </is>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>ReconstructItinerary.java</t>
+          <t>EarliestMomentEveryoneFriends.java</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
@@ -6810,25 +6810,25 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Network Delay Time</t>
+          <t>Word Ladder</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>743</v>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F131" s="15" t="inlineStr">
-        <is>
-          <t>L6 differentiator</t>
+        <v>127</v>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>LC 743</t>
+          <t>LC 127</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>NetworkDelayTime.java</t>
+          <t>WordLadder.java</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
@@ -6858,25 +6858,25 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Detonate the Maximum Bombs</t>
+          <t>Shortest Distance from All Buildings</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2101</v>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F132" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>317</v>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>LC 2101</t>
+          <t>LC 317</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>DetonateTheMaximumBombs.java</t>
+          <t>ShortestDistanceFromAllBuildings.java</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
@@ -6906,25 +6906,25 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Minimum Time to Visit a Cell In a Grid</t>
+          <t>Swim in Rising Water</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2577</v>
+        <v>778</v>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>LC 2577</t>
+          <t>LC 778</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>MinimumTimeToVisitCell.java</t>
+          <t>SwimInRisingWater.java</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
@@ -6954,25 +6954,25 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Number of Good Paths</t>
+          <t>Cheapest Flights Within K Stops</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2421</v>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F134" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>787</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>LC 2421</t>
+          <t>LC 787</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>NumberOfGoodPaths.java</t>
+          <t>CheapestFlightsWithinKStops.java</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
@@ -7002,25 +7002,25 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Critical Connections in a Network</t>
+          <t>Race Car</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1192</v>
+        <v>818</v>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F135" s="15" t="inlineStr">
-        <is>
-          <t>L6 differentiator</t>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>LC 1192</t>
+          <t>LC 818</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>CriticalConnections.java</t>
+          <t>RaceCar.java</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
@@ -7050,25 +7050,25 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>🚀 Advanced Graphs (L6)</t>
+          <t>🕸️ Graphs</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Cat and Mouse</t>
+          <t>Reconstruct Itinerary</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>913</v>
+        <v>332</v>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F136" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>LC 913</t>
+          <t>LC 332</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>CatAndMouse.java</t>
+          <t>ReconstructItinerary.java</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
@@ -7098,25 +7098,25 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>🤑 Greedy</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Gas Station</t>
+          <t>Network Delay Time</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>134</v>
+        <v>743</v>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F137" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F137" s="15" t="inlineStr">
+        <is>
+          <t>L6 differentiator</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>LC 134</t>
+          <t>LC 743</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GasStation.java</t>
+          <t>NetworkDelayTime.java</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
@@ -7146,25 +7146,25 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>🤑 Greedy</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Task Scheduler</t>
+          <t>Detonate the Maximum Bombs</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>621</v>
+        <v>2101</v>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F138" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>LC 621</t>
+          <t>LC 2101</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>TaskScheduler.java</t>
+          <t>DetonateTheMaximumBombs.java</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
@@ -7194,27 +7194,25 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>🤑 Greedy</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Huffman Coding</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Minimum Time to Visit a Cell In a Grid</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>2577</v>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F139" s="16" t="inlineStr">
-        <is>
-          <t>Reported L6</t>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7222,14 +7220,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>LC 2577</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>HuffmanCoding.java</t>
+          <t>MinimumTimeToVisitCell.java</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -7244,25 +7242,25 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Climbing Stairs</t>
+          <t>Number of Good Paths</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>2421</v>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7272,12 +7270,12 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>LC 70</t>
+          <t>LC 2421</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>ClimbingStairs.java</t>
+          <t>NumberOfGoodPaths.java</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
@@ -7292,25 +7290,25 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>House Robber</t>
+          <t>Critical Connections in a Network</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>1192</v>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F141" s="15" t="inlineStr">
+        <is>
+          <t>L6 differentiator</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -7320,12 +7318,12 @@
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>LC 198</t>
+          <t>LC 1192</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>HouseRobber.java</t>
+          <t>CriticalConnections.java</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr">
@@ -7340,25 +7338,25 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🚀 Advanced Graphs (L6)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>House Robber II</t>
+          <t>Cat and Mouse</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+        <v>913</v>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F142" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -7368,12 +7366,12 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>LC 213</t>
+          <t>LC 913</t>
         </is>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>HouseRobberII.java</t>
+          <t>CatAndMouse.java</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
@@ -7388,25 +7386,25 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🤑 Greedy</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Jump Game</t>
+          <t>Gas Station</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -7416,12 +7414,12 @@
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>LC 55</t>
+          <t>LC 134</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>JumpGame.java</t>
+          <t>GasStation.java</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -7436,25 +7434,25 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🤑 Greedy</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Jump Game II</t>
+          <t>Task Scheduler</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>45</v>
+        <v>621</v>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -7464,12 +7462,12 @@
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>LC 45</t>
+          <t>LC 621</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>JumpGameII.java</t>
+          <t>TaskScheduler.java</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
@@ -7484,25 +7482,27 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>📐 Dynamic Programming</t>
+          <t>🤑 Greedy</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Coin Change</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>322</v>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+          <t>Huffman Coding</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
+        <is>
+          <t>Reported L6</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -7510,14 +7510,14 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>LC 322</t>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>CoinChange.java</t>
+          <t>HuffmanCoding.java</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
@@ -7537,20 +7537,20 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Coin Change II</t>
+          <t>Climbing Stairs</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>518</v>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>70</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>LC 518</t>
+          <t>LC 70</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>CoinChangeII.java</t>
+          <t>ClimbingStairs.java</t>
         </is>
       </c>
       <c r="J146" s="5" t="inlineStr">
@@ -7585,11 +7585,11 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Word Break</t>
+          <t>House Robber</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
@@ -7608,12 +7608,12 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>LC 139</t>
+          <t>LC 198</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>WordBreak.java</t>
+          <t>HouseRobber.java</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
@@ -7633,11 +7633,11 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Decode Ways</t>
+          <t>House Robber II</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>91</v>
+        <v>213</v>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>LC 91</t>
+          <t>LC 213</t>
         </is>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>DecodeWays.java</t>
+          <t>HouseRobberII.java</t>
         </is>
       </c>
       <c r="J148" s="5" t="inlineStr">
@@ -7681,20 +7681,20 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Longest Increasing Subsequence</t>
+          <t>Jump Game</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F149" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -7704,12 +7704,12 @@
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>LC 300</t>
+          <t>LC 55</t>
         </is>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>LongestIncreasingSubsequence.java</t>
+          <t>JumpGame.java</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr">
@@ -7729,20 +7729,20 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Unique Paths</t>
+          <t>Jump Game II</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>Core</t>
+      <c r="F150" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>LC 62</t>
+          <t>LC 45</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>UniquePaths.java</t>
+          <t>JumpGameII.java</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr">
@@ -7777,20 +7777,20 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Unique Paths II</t>
+          <t>Coin Change</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>63</v>
+        <v>322</v>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F151" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>LC 63</t>
+          <t>LC 322</t>
         </is>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>UniquePathsII.java</t>
+          <t>CoinChange.java</t>
         </is>
       </c>
       <c r="J151" s="5" t="inlineStr">
@@ -7825,20 +7825,20 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Maximal Square</t>
+          <t>Coin Change II</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>221</v>
+        <v>518</v>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F152" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>LC 221</t>
+          <t>LC 518</t>
         </is>
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>MaximalSquare.java</t>
+          <t>CoinChangeII.java</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -7873,11 +7873,11 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Longest Common Subsequence</t>
+          <t>Word Break</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1143</v>
+        <v>139</v>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>LC 1143</t>
+          <t>LC 139</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>LongestCommonSubsequence.java</t>
+          <t>WordBreak.java</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
@@ -7921,20 +7921,20 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Edit Distance</t>
+          <t>Decode Ways</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F154" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>LC 72</t>
+          <t>LC 91</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>EditDistance.java</t>
+          <t>DecodeWays.java</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
@@ -7969,20 +7969,20 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Student Attendance Record II</t>
+          <t>Longest Increasing Subsequence</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>552</v>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F155" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>300</v>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F155" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>LC 552</t>
+          <t>LC 300</t>
         </is>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>StudentAttendanceRecordII.java</t>
+          <t>LongestIncreasingSubsequence.java</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr">
@@ -8017,20 +8017,20 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Poor Pigs</t>
+          <t>Unique Paths</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>458</v>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>62</v>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>LC 458</t>
+          <t>LC 62</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>PoorPigs.java</t>
+          <t>UniquePaths.java</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr">
@@ -8065,20 +8065,20 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Numbers At Most N Given Digit Set</t>
+          <t>Unique Paths II</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>902</v>
-      </c>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F157" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>63</v>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>LC 902</t>
+          <t>LC 63</t>
         </is>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>NumbersAtMostNGivenDigitSet.java</t>
+          <t>UniquePathsII.java</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
@@ -8108,25 +8108,25 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Counting Bits</t>
+          <t>Maximal Square</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F158" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>221</v>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>LC 338</t>
+          <t>LC 221</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>CountingBits.java</t>
+          <t>MaximalSquare.java</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -8156,25 +8156,25 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Sum of Two Integers</t>
+          <t>Longest Common Subsequence</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>371</v>
+        <v>1143</v>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F159" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>LC 371</t>
+          <t>LC 1143</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>SumOfTwoIntegers.java</t>
+          <t>LongestCommonSubsequence.java</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
@@ -8204,16 +8204,16 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Pow(x, n)</t>
+          <t>Edit Distance</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>LC 50</t>
+          <t>LC 72</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>PowXN.java</t>
+          <t>EditDistance.java</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
@@ -8252,25 +8252,25 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Linked List Random Node</t>
+          <t>Student Attendance Record II</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>382</v>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F161" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>552</v>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>LC 382</t>
+          <t>LC 552</t>
         </is>
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>LinkedListRandomNode.java</t>
+          <t>StudentAttendanceRecordII.java</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
@@ -8300,25 +8300,25 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Random Pick with Weight</t>
+          <t>Poor Pigs</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>528</v>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F162" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>458</v>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>LC 528</t>
+          <t>LC 458</t>
         </is>
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>RandomPickWithWeight.java</t>
+          <t>PoorPigs.java</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr">
@@ -8348,20 +8348,20 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>🔢 Bit &amp; Math</t>
+          <t>📐 Dynamic Programming</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Numbers At Most N Given Digit Set</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>902</v>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F163" s="12" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>LC 204</t>
+          <t>LC 902</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>CountPrimes.java</t>
+          <t>NumbersAtMostNGivenDigitSet.java</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
@@ -8401,20 +8401,20 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Greatest Common Divisor of Strings</t>
+          <t>Counting Bits</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>1071</v>
+        <v>338</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F164" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>LC 1071</t>
+          <t>LC 338</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>GreatestCommonDivisorOfStrings.java</t>
+          <t>CountingBits.java</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
@@ -8449,20 +8449,20 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Maximum XOR of Two Numbers in an Array</t>
+          <t>Sum of Two Integers</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>421</v>
+        <v>371</v>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F165" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>LC 421</t>
+          <t>LC 371</t>
         </is>
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>MaximumXorOfTwoNumbers.java</t>
+          <t>SumOfTwoIntegers.java</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
@@ -8492,16 +8492,16 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>🌴 Segment Tree / BIT</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Range Sum Query - Mutable</t>
+          <t>Pow(x, n)</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>307</v>
+        <v>50</v>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>LC 307</t>
+          <t>LC 50</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>RangeSumQueryMutable.java</t>
+          <t>PowXN.java</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
@@ -8540,25 +8540,25 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>🌴 Segment Tree / BIT</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Count of Range Sum</t>
+          <t>Linked List Random Node</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F167" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>382</v>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>LC 327</t>
+          <t>LC 382</t>
         </is>
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>CountOfRangeSum.java</t>
+          <t>LinkedListRandomNode.java</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
@@ -8588,25 +8588,25 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Min Stack</t>
+          <t>Random Pick with Weight</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>155</v>
+        <v>528</v>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F168" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="H168" s="5" t="inlineStr">
         <is>
-          <t>LC 155</t>
+          <t>LC 528</t>
         </is>
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>MinStack.java</t>
+          <t>RandomPickWithWeight.java</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
@@ -8636,25 +8636,25 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Stock Price Fluctuation</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>2034</v>
+        <v>204</v>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F169" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>LC 2034</t>
+          <t>LC 204</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>StockPriceFluctuation.java</t>
+          <t>CountPrimes.java</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
@@ -8684,25 +8684,25 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Detect Squares</t>
+          <t>Greatest Common Divisor of Strings</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F170" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+        <v>1071</v>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>LC 2013</t>
+          <t>LC 1071</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>DetectSquares.java</t>
+          <t>GreatestCommonDivisorOfStrings.java</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
@@ -8732,25 +8732,25 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🔢 Bit &amp; Math</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Design Twitter</t>
+          <t>Maximum XOR of Two Numbers in an Array</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>355</v>
+        <v>421</v>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F171" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>LC 355</t>
+          <t>LC 421</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>DesignTwitter.java</t>
+          <t>MaximumXorOfTwoNumbers.java</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
@@ -8780,25 +8780,25 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🌴 Segment Tree / BIT</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>LFU Cache</t>
+          <t>Range Sum Query - Mutable</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>460</v>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>307</v>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>LC 460</t>
+          <t>LC 307</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>LFUCache.java</t>
+          <t>RangeSumQueryMutable.java</t>
         </is>
       </c>
       <c r="J172" s="5" t="inlineStr">
@@ -8828,25 +8828,25 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>🏗️ Design</t>
+          <t>🌴 Segment Tree / BIT</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Snapshot Array</t>
+          <t>Count of Range Sum</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>1146</v>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>327</v>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>LC 1146</t>
+          <t>LC 327</t>
         </is>
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>SnapshotArray.java</t>
+          <t>CountOfRangeSum.java</t>
         </is>
       </c>
       <c r="J173" s="5" t="inlineStr">
@@ -8881,20 +8881,20 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Insert Delete GetRandom O(1)</t>
+          <t>Min Stack</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>380</v>
+        <v>155</v>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F174" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>LC 380</t>
+          <t>LC 155</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>InsertDeleteGetRandomO1.java</t>
+          <t>MinStack.java</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
@@ -8929,20 +8929,20 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Time Based Key-Value Store</t>
+          <t>Stock Price Fluctuation</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>981</v>
+        <v>2034</v>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F175" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F175" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>LC 981</t>
+          <t>LC 2034</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>TimeBasedKeyValueStore.java</t>
+          <t>StockPriceFluctuation.java</t>
         </is>
       </c>
       <c r="J175" s="5" t="inlineStr">
@@ -8977,11 +8977,11 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Design Hit Counter</t>
+          <t>Detect Squares</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>362</v>
+        <v>2013</v>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>LC 362</t>
+          <t>LC 2013</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>DesignHitCounter.java</t>
+          <t>DetectSquares.java</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
@@ -9020,25 +9020,25 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>🎭 Bitmask / Subset DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Shortest Path Visiting All Nodes</t>
+          <t>Design Twitter</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>847</v>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F177" s="14" t="inlineStr">
-        <is>
-          <t>Staff-tagged</t>
+        <v>355</v>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>LC 847</t>
+          <t>LC 355</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>ShortestPathVisitingAllNodes.java</t>
+          <t>DesignTwitter.java</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
@@ -9068,25 +9068,25 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>🎭 Bitmask / Subset DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Partition to K Equal Sum Subsets</t>
+          <t>LFU Cache</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F178" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>460</v>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>LC 698</t>
+          <t>LC 460</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>PartitionToKEqualSumSubsets.java</t>
+          <t>LFUCache.java</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
@@ -9116,25 +9116,25 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>🎭 Bitmask / Subset DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Smallest Sufficient Team</t>
+          <t>Snapshot Array</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1125</v>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F179" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>1146</v>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>LC 1125</t>
+          <t>LC 1146</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>SmallestSufficientTeam.java</t>
+          <t>SnapshotArray.java</t>
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr">
@@ -9164,25 +9164,25 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>🎈 Interval DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Burst Balloons</t>
+          <t>Insert Delete GetRandom O(1)</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>312</v>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>380</v>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F180" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -9192,12 +9192,12 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>LC 312</t>
+          <t>LC 380</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>BurstBalloons.java</t>
+          <t>InsertDeleteGetRandomO1.java</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
@@ -9212,25 +9212,25 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>🎈 Interval DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Stone Game</t>
+          <t>Time Based Key-Value Store</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>877</v>
+        <v>981</v>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F181" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>LC 877</t>
+          <t>LC 981</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>StoneGame.java</t>
+          <t>TimeBasedKeyValueStore.java</t>
         </is>
       </c>
       <c r="J181" s="5" t="inlineStr">
@@ -9260,25 +9260,25 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>🎈 Interval DP</t>
+          <t>🏗️ Design</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Minimum Cost to Cut a Stick</t>
+          <t>Design Hit Counter</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1547</v>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F182" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>362</v>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F182" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>LC 1547</t>
+          <t>LC 362</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>MinimumCostToCutAStick.java</t>
+          <t>DesignHitCounter.java</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
@@ -9308,25 +9308,25 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
+          <t>🎭 Bitmask / Subset DP</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Partition Equal Subset Sum</t>
+          <t>Shortest Path Visiting All Nodes</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>416</v>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F183" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+        <v>847</v>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F183" s="14" t="inlineStr">
+        <is>
+          <t>Staff-tagged</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>LC 416</t>
+          <t>LC 847</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>PartitionEqualSubsetSum.java</t>
+          <t>ShortestPathVisitingAllNodes.java</t>
         </is>
       </c>
       <c r="J183" s="5" t="inlineStr">
@@ -9356,25 +9356,25 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
+          <t>🎭 Bitmask / Subset DP</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Target Sum</t>
+          <t>Partition to K Equal Sum Subsets</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>494</v>
+        <v>698</v>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F184" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>LC 494</t>
+          <t>LC 698</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>TargetSum.java</t>
+          <t>PartitionToKEqualSumSubsets.java</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
@@ -9404,20 +9404,20 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>🌉 Minimum Spanning Tree</t>
+          <t>🎭 Bitmask / Subset DP</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Min Cost to Connect All Points</t>
+          <t>Smallest Sufficient Team</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E185" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+        <v>1125</v>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>LC 1584</t>
+          <t>LC 1125</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>MinCostToConnectAllPoints.java</t>
+          <t>SmallestSufficientTeam.java</t>
         </is>
       </c>
       <c r="J185" s="5" t="inlineStr">
@@ -9452,25 +9452,25 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>🌉 Minimum Spanning Tree</t>
+          <t>🎈 Interval DP</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Connecting Cities With Minimum Cost</t>
+          <t>Burst Balloons</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1135</v>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F186" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>312</v>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>LC 1135</t>
+          <t>LC 312</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>ConnectingCitiesWithMinimumCost.java</t>
+          <t>BurstBalloons.java</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr">
@@ -9500,25 +9500,25 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>🧬 String Matching</t>
+          <t>🎈 Interval DP</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Repeated DNA Sequences</t>
+          <t>Stone Game</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>187</v>
+        <v>877</v>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
-        <is>
-          <t>Google-tagged</t>
+      <c r="F187" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>LC 187</t>
+          <t>LC 877</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>RepeatedDNASequences.java</t>
+          <t>StoneGame.java</t>
         </is>
       </c>
       <c r="J187" s="5" t="inlineStr">
@@ -9548,25 +9548,25 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>🧬 String Matching</t>
+          <t>🎈 Interval DP</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Shortest Palindrome</t>
+          <t>Minimum Cost to Cut a Stick</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>214</v>
+        <v>1547</v>
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F188" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>LC 214</t>
+          <t>LC 1547</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>ShortestPalindrome.java</t>
+          <t>MinimumCostToCutAStick.java</t>
         </is>
       </c>
       <c r="J188" s="5" t="inlineStr">
@@ -9596,25 +9596,25 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>🧬 String Matching</t>
+          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Longest Duplicate Substring</t>
+          <t>Partition Equal Subset Sum</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>1044</v>
-      </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F189" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>416</v>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>LC 1044</t>
+          <t>LC 416</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>LongestDuplicateSubstring.java</t>
+          <t>PartitionEqualSubsetSum.java</t>
         </is>
       </c>
       <c r="J189" s="5" t="inlineStr">
@@ -9644,25 +9644,25 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>🎄 Tree DP / Rerooting</t>
+          <t>🎒 0/1 Knapsack &amp; Subset-Sum</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>House Robber III</t>
+          <t>Target Sum</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>337</v>
+        <v>494</v>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>Google fav</t>
+      <c r="F190" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>LC 337</t>
+          <t>LC 494</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>HouseRobberIII.java</t>
+          <t>TargetSum.java</t>
         </is>
       </c>
       <c r="J190" s="5" t="inlineStr">
@@ -9692,20 +9692,20 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>🎄 Tree DP / Rerooting</t>
+          <t>🌉 Minimum Spanning Tree</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Binary Tree Cameras</t>
+          <t>Min Cost to Connect All Points</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>968</v>
-      </c>
-      <c r="E191" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>1584</v>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>LC 968</t>
+          <t>LC 1584</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>BinaryTreeCameras.java</t>
+          <t>MinCostToConnectAllPoints.java</t>
         </is>
       </c>
       <c r="J191" s="5" t="inlineStr">
@@ -9740,25 +9740,25 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>🎄 Tree DP / Rerooting</t>
+          <t>🌉 Minimum Spanning Tree</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Sum of Distances in Tree</t>
+          <t>Connecting Cities With Minimum Cost</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>834</v>
-      </c>
-      <c r="E192" s="7" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F192" s="11" t="inlineStr">
-        <is>
-          <t>Google signature</t>
+        <v>1135</v>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>LC 834</t>
+          <t>LC 1135</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>SumOfDistancesInTree.java</t>
+          <t>ConnectingCitiesWithMinimumCost.java</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr">
@@ -9788,25 +9788,25 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>📊 2D Prefix Sum</t>
+          <t>🧬 String Matching</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Range Sum Query 2D - Immutable</t>
+          <t>Repeated DNA Sequences</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F193" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F193" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>LC 304</t>
+          <t>LC 187</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>RangeSumQuery2DImmutable.java</t>
+          <t>RepeatedDNASequences.java</t>
         </is>
       </c>
       <c r="J193" s="5" t="inlineStr">
@@ -9836,25 +9836,25 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>📊 2D Prefix Sum</t>
+          <t>🧬 String Matching</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Range Sum Query 2D - Mutable</t>
+          <t>Shortest Palindrome</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>308</v>
+        <v>214</v>
       </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F194" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>LC 308</t>
+          <t>LC 214</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>RangeSumQuery2DMutable.java</t>
+          <t>ShortestPalindrome.java</t>
         </is>
       </c>
       <c r="J194" s="5" t="inlineStr">
@@ -9884,25 +9884,25 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>➕ Difference Array</t>
+          <t>🧬 String Matching</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Longest Duplicate Substring</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1109</v>
-      </c>
-      <c r="E195" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F195" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+        <v>1044</v>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>LC 1109</t>
+          <t>LC 1044</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>CorporateFlightBookings.java</t>
+          <t>LongestDuplicateSubstring.java</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
@@ -9932,25 +9932,25 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>➕ Difference Array</t>
+          <t>🎄 Tree DP / Rerooting</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Car Pooling</t>
+          <t>House Robber III</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>1094</v>
+        <v>337</v>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F196" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F196" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>LC 1094</t>
+          <t>LC 337</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>CarPooling.java</t>
+          <t>HouseRobberIII.java</t>
         </is>
       </c>
       <c r="J196" s="5" t="inlineStr">
@@ -9980,25 +9980,25 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>🗂️ Ordered-Set / Stream</t>
+          <t>🎄 Tree DP / Rerooting</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Contains Duplicate III</t>
+          <t>Binary Tree Cameras</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>220</v>
+        <v>968</v>
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F197" s="12" t="inlineStr">
-        <is>
-          <t>Gap-fill</t>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>LC 220</t>
+          <t>LC 968</t>
         </is>
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>ContainsDuplicateIII.java</t>
+          <t>BinaryTreeCameras.java</t>
         </is>
       </c>
       <c r="J197" s="5" t="inlineStr">
@@ -10028,52 +10028,724 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
+          <t>🎄 Tree DP / Rerooting</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Sum of Distances in Tree</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>LC 834</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>SumOfDistancesInTree.java</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>📊 2D Prefix Sum</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Range Sum Query 2D - Immutable</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>LC 304</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>RangeSumQuery2DImmutable.java</t>
+        </is>
+      </c>
+      <c r="J199" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>📊 2D Prefix Sum</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Range Sum Query 2D - Mutable</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>LC 308</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="inlineStr">
+        <is>
+          <t>RangeSumQuery2DMutable.java</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>➕ Difference Array</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Flight Bookings</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F201" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>LC 1109</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="inlineStr">
+        <is>
+          <t>CorporateFlightBookings.java</t>
+        </is>
+      </c>
+      <c r="J201" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>➕ Difference Array</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Car Pooling</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F202" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>LC 1094</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>CarPooling.java</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
           <t>🗂️ Ordered-Set / Stream</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Contains Duplicate III</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F203" s="12" t="inlineStr">
+        <is>
+          <t>Gap-fill</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>LC 220</t>
+        </is>
+      </c>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>ContainsDuplicateIII.java</t>
+        </is>
+      </c>
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>🗂️ Ordered-Set / Stream</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Sliding Window Median</t>
         </is>
       </c>
-      <c r="D198" s="2" t="n">
+      <c r="D204" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="E198" s="7" t="inlineStr">
+      <c r="E204" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F198" s="10" t="inlineStr">
+      <c r="F204" s="10" t="inlineStr">
         <is>
           <t>Google-tagged</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H198" s="5" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
         <is>
           <t>LC 480</t>
         </is>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="I204" s="5" t="inlineStr">
         <is>
           <t>SlidingWindowMedian.java</t>
         </is>
       </c>
-      <c r="J198" s="5" t="inlineStr">
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Sort an Array</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>LC 912</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>SortAnArray.java</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Largest Number</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F206" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>LC 179</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="inlineStr">
+        <is>
+          <t>LargestNumber.java</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Pancake Sorting</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>969</v>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>LC 969</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="inlineStr">
+        <is>
+          <t>PancakeSorting.java</t>
+        </is>
+      </c>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Maximum Gap</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>LC 164</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>MaximumGap.java</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Wiggle Sort II</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>LC 324</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="inlineStr">
+        <is>
+          <t>WiggleSortII.java</t>
+        </is>
+      </c>
+      <c r="J209" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>🪢 Topological Sort</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Course Schedule II</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F210" s="8" t="inlineStr">
+        <is>
+          <t>Google fav</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>LC 210</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="inlineStr">
+        <is>
+          <t>CourseScheduleII.java</t>
+        </is>
+      </c>
+      <c r="J210" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>🪢 Topological Sort</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Minimum Height Trees</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F211" s="10" t="inlineStr">
+        <is>
+          <t>Google-tagged</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>LC 310</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>MinimumHeightTrees.java</t>
+        </is>
+      </c>
+      <c r="J211" s="5" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>🪢 Topological Sort</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Sort Items by Groups Respecting Dependencies</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>Google signature</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>LC 1203</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>SortItemsByGroups.java</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J198"/>
+  <autoFilter ref="A1:J212"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G198" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Studying,Solved,Review"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10488,24 +11160,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId408"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId409"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId428"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId429"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId431"/>
@@ -10667,6 +11339,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId587"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId588"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId631"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11361,7 +12075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C53"/>
+  <dimension ref="B2:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -11382,7 +12096,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -11410,7 +12124,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -11420,7 +12134,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -11468,7 +12182,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -11478,7 +12192,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -11488,7 +12202,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -11498,7 +12212,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -11606,7 +12320,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -11837,6 +12551,26 @@
       </c>
       <c r="C53" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>🔃 Sorting Algorithms</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>🪢 Topological Sort</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
